--- a/output/pdf_financials_xlsx/OILS.xlsx
+++ b/output/pdf_financials_xlsx/OILS.xlsx
@@ -1908,13 +1908,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>4.14574</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.740295</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.697277</v>
       </c>
     </row>
     <row r="93">
@@ -3211,7 +3211,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -3422,7 +3426,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" s="5" t="n">
         <v>4.14574</v>
       </c>

--- a/output/pdf_financials_xlsx/OILS.xlsx
+++ b/output/pdf_financials_xlsx/OILS.xlsx
@@ -968,13 +968,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.898899</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.438536</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.446563</v>
       </c>
     </row>
     <row r="35">
@@ -1000,13 +1000,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.898899</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.438536</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.446563</v>
       </c>
     </row>
     <row r="37">
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.555329</v>
+        <v>1.65643</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.389843</v>
+        <v>1.951307</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.352946</v>
+        <v>0.906383</v>
       </c>
     </row>
     <row r="49">
@@ -2411,13 +2411,13 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.08303099999999999</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.121882</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.13906</v>
       </c>
     </row>
     <row r="125">
@@ -2427,13 +2427,13 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.08303099999999999</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.121882</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.13906</v>
       </c>
     </row>
     <row r="126">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -4065,7 +4065,11 @@
           <t>Lease payments 5</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E48" s="5" t="n">
         <v>-0.08303099999999999</v>
       </c>
